--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6672,0.2971,0.0889,0.0218</t>
-  </si>
-  <si>
-    <t>0.1187,0.0266,0.0382,0.8938</t>
-  </si>
-  <si>
-    <t>0.6648,0.1728,0.0153,0.1337</t>
-  </si>
-  <si>
-    <t>0.5650,0.0950,0.0772,0.3290</t>
-  </si>
-  <si>
-    <t>0.9906,0.0080,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9945,0.0040,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9645,0.0313,0.0074,0.0032</t>
-  </si>
-  <si>
-    <t>0.9868,0.0092,0.0010,0.0022</t>
-  </si>
-  <si>
-    <t>0.9947,0.0043,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9878,0.0074,0.0011,0.0022</t>
-  </si>
-  <si>
-    <t>0.9672,0.0435,0.0025,0.0021</t>
-  </si>
-  <si>
-    <t>0.9739,0.0245,0.0032,0.0028</t>
-  </si>
-  <si>
-    <t>0.3646,0.5048,0.2408,0.0188</t>
-  </si>
-  <si>
-    <t>0.1163,0.1457,0.8209,0.0038</t>
-  </si>
-  <si>
-    <t>0.3422,0.2205,0.4814,0.0188</t>
-  </si>
-  <si>
-    <t>0.0432,0.6423,0.6304,0.0050</t>
-  </si>
-  <si>
-    <t>0.4730,0.1862,0.3650,0.0204</t>
-  </si>
-  <si>
-    <t>0.0258,0.9708,0.0279,0.0012</t>
-  </si>
-  <si>
-    <t>0.0647,0.9421,0.0316,0.0014</t>
-  </si>
-  <si>
-    <t>0.4202,0.7027,0.0198,0.0033</t>
-  </si>
-  <si>
-    <t>0.0733,0.9446,0.0133,0.0013</t>
-  </si>
-  <si>
-    <t>0.0133,0.9842,0.0197,0.0004</t>
-  </si>
-  <si>
-    <t>0.2672,0.1331,0.6577,0.0193</t>
-  </si>
-  <si>
-    <t>0.1828,0.0796,0.7910,0.0077</t>
-  </si>
-  <si>
-    <t>0.0397,0.3814,0.8331,0.0084</t>
-  </si>
-  <si>
-    <t>0.1810,0.4486,0.5034,0.0487</t>
-  </si>
-  <si>
-    <t>0.0997,0.1037,0.8653,0.0045</t>
-  </si>
-  <si>
-    <t>0.2576,0.0552,0.7438,0.0220</t>
-  </si>
-  <si>
-    <t>0.0308,0.0824,0.9491,0.0036</t>
-  </si>
-  <si>
-    <t>0.4400,0.6580,0.0292,0.0062</t>
-  </si>
-  <si>
-    <t>0.1359,0.8154,0.1277,0.0119</t>
-  </si>
-  <si>
-    <t>0.0113,0.0258,0.9811,0.0032</t>
-  </si>
-  <si>
-    <t>0.0828,0.7805,0.2603,0.0064</t>
-  </si>
-  <si>
-    <t>0.6313,0.4446,0.0320,0.0123</t>
-  </si>
-  <si>
-    <t>0.1905,0.8030,0.0497,0.0064</t>
-  </si>
-  <si>
-    <t>0.4055,0.6960,0.0172,0.0047</t>
-  </si>
-  <si>
-    <t>0.2110,0.7278,0.1515,0.0115</t>
-  </si>
-  <si>
-    <t>0.0008,0.9830,0.4632,0.0004</t>
-  </si>
-  <si>
-    <t>0.0051,0.7555,0.9137,0.0007</t>
-  </si>
-  <si>
-    <t>0.0109,0.7807,0.8387,0.0021</t>
-  </si>
-  <si>
-    <t>0.0497,0.1507,0.9096,0.0042</t>
-  </si>
-  <si>
-    <t>0.0091,0.6975,0.8770,0.0009</t>
-  </si>
-  <si>
-    <t>0.0026,0.9713,0.3526,0.0008</t>
-  </si>
-  <si>
-    <t>0.0385,0.5621,0.7666,0.0076</t>
-  </si>
-  <si>
-    <t>0.2518,0.1513,0.0887,0.7264</t>
-  </si>
-  <si>
-    <t>0.0073,0.9846,0.0148,0.0026</t>
-  </si>
-  <si>
-    <t>0.0021,0.9936,0.0209,0.0004</t>
-  </si>
-  <si>
-    <t>0.0029,0.9935,0.0157,0.0005</t>
-  </si>
-  <si>
-    <t>0.0055,0.8050,0.8398,0.0026</t>
-  </si>
-  <si>
-    <t>0.0048,0.6160,0.9448,0.0007</t>
-  </si>
-  <si>
-    <t>0.2844,0.1763,0.6242,0.0373</t>
-  </si>
-  <si>
-    <t>0.2004,0.0824,0.7795,0.0180</t>
-  </si>
-  <si>
-    <t>0.0137,0.3461,0.9368,0.0023</t>
-  </si>
-  <si>
-    <t>0.0196,0.2496,0.9396,0.0022</t>
-  </si>
-  <si>
-    <t>0.9888,0.0083,0.0009,0.0017</t>
-  </si>
-  <si>
-    <t>0.9889,0.0046,0.0008,0.0034</t>
-  </si>
-  <si>
-    <t>0.9859,0.0119,0.0011,0.0019</t>
-  </si>
-  <si>
-    <t>0.1187,0.2226,0.7686,0.0125</t>
-  </si>
-  <si>
-    <t>0.9751,0.0210,0.0026,0.0035</t>
-  </si>
-  <si>
-    <t>0.8989,0.1583,0.0066,0.0027</t>
-  </si>
-  <si>
-    <t>0.9865,0.0132,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.0018,0.9570,0.6915,0.0008</t>
-  </si>
-  <si>
-    <t>0.0095,0.6300,0.9053,0.0020</t>
-  </si>
-  <si>
-    <t>0.0089,0.7285,0.8836,0.0022</t>
-  </si>
-  <si>
-    <t>0.0007,0.9665,0.7966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.3481,0.9752,0.0005</t>
-  </si>
-  <si>
-    <t>0.0300,0.9486,0.0827,0.0019</t>
-  </si>
-  <si>
-    <t>0.0020,0.9965,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.7210,0.0832,0.2163,0.0446</t>
-  </si>
-  <si>
-    <t>0.1367,0.7510,0.1845,0.0054</t>
-  </si>
-  <si>
-    <t>0.0677,0.2584,0.8247,0.0076</t>
-  </si>
-  <si>
-    <t>0.0009,0.9223,0.9044,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.9653,0.7109,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.9761,0.2915,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9406,0.7776,0.0006</t>
-  </si>
-  <si>
-    <t>0.0197,0.0162,0.0370,0.9637</t>
-  </si>
-  <si>
-    <t>0.0147,0.0131,0.0040,0.9872</t>
-  </si>
-  <si>
-    <t>0.0200,0.0228,0.0333,0.9653</t>
-  </si>
-  <si>
-    <t>0.0199,0.0317,0.0142,0.9750</t>
-  </si>
-  <si>
-    <t>0.0578,0.0679,0.0389,0.9218</t>
-  </si>
-  <si>
-    <t>0.0327,0.0385,0.0094,0.9672</t>
-  </si>
-  <si>
-    <t>0.0011,0.9689,0.7367,0.0003</t>
-  </si>
-  <si>
-    <t>0.0014,0.8738,0.9425,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.7986,0.9525,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.8379,0.9129,0.0005</t>
-  </si>
-  <si>
-    <t>0.0009,0.9559,0.8412,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.8962,0.8729,0.0006</t>
-  </si>
-  <si>
-    <t>0.9832,0.0113,0.0025,0.0024</t>
-  </si>
-  <si>
-    <t>0.9886,0.0125,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9860,0.0151,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.9911,0.0078,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9897,0.0076,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.9905,0.0088,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9849,0.0097,0.0010,0.0029</t>
-  </si>
-  <si>
-    <t>0.9906,0.0069,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9862,0.0097,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9840,0.0178,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.9902,0.0058,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9903,0.0085,0.0007,0.0013</t>
-  </si>
-  <si>
-    <t>0.9887,0.0100,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9873,0.0124,0.0012,0.0014</t>
-  </si>
-  <si>
-    <t>0.9891,0.0087,0.0008,0.0021</t>
-  </si>
-  <si>
-    <t>0.9918,0.0036,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.0222,0.0407,0.9662,0.0066</t>
-  </si>
-  <si>
-    <t>0.0261,0.0755,0.9582,0.0011</t>
-  </si>
-  <si>
-    <t>0.4222,0.1390,0.5133,0.0515</t>
-  </si>
-  <si>
-    <t>0.2690,0.1059,0.6966,0.0373</t>
-  </si>
-  <si>
-    <t>0.1258,0.8969,0.0256,0.0017</t>
-  </si>
-  <si>
-    <t>0.0767,0.9385,0.0185,0.0011</t>
-  </si>
-  <si>
-    <t>0.2405,0.8629,0.0074,0.0019</t>
-  </si>
-  <si>
-    <t>0.5294,0.5772,0.0289,0.0027</t>
-  </si>
-  <si>
-    <t>0.0645,0.9408,0.0226,0.0012</t>
-  </si>
-  <si>
-    <t>0.0578,0.9561,0.0109,0.0007</t>
-  </si>
-  <si>
-    <t>0.2882,0.7724,0.0311,0.0030</t>
-  </si>
-  <si>
-    <t>0.2156,0.5554,0.3170,0.0104</t>
-  </si>
-  <si>
-    <t>0.1352,0.3156,0.6395,0.0070</t>
-  </si>
-  <si>
-    <t>0.1484,0.7363,0.1744,0.0192</t>
-  </si>
-  <si>
-    <t>0.2963,0.2560,0.5062,0.0109</t>
-  </si>
-  <si>
-    <t>0.5522,0.2826,0.2150,0.0953</t>
-  </si>
-  <si>
-    <t>0.0044,0.9898,0.0295,0.0006</t>
-  </si>
-  <si>
-    <t>0.0120,0.9719,0.0645,0.0021</t>
-  </si>
-  <si>
-    <t>0.1115,0.8689,0.0663,0.0118</t>
-  </si>
-  <si>
-    <t>0.0020,0.9935,0.0331,0.0005</t>
-  </si>
-  <si>
-    <t>0.0947,0.8752,0.0977,0.0027</t>
-  </si>
-  <si>
-    <t>0.5754,0.4349,0.0576,0.0041</t>
-  </si>
-  <si>
-    <t>0.2308,0.8348,0.0199,0.0021</t>
-  </si>
-  <si>
-    <t>0.9642,0.0256,0.0058,0.0044</t>
-  </si>
-  <si>
-    <t>0.9901,0.0042,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.9610,0.0281,0.0022,0.0066</t>
-  </si>
-  <si>
-    <t>0.8738,0.1485,0.0133,0.0076</t>
-  </si>
-  <si>
-    <t>0.9876,0.0113,0.0012,0.0017</t>
-  </si>
-  <si>
-    <t>0.8971,0.1637,0.0084,0.0027</t>
-  </si>
-  <si>
-    <t>0.9479,0.0517,0.0059,0.0050</t>
-  </si>
-  <si>
-    <t>0.9848,0.0103,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.0028,0.9423,0.7102,0.0009</t>
-  </si>
-  <si>
-    <t>0.0022,0.9432,0.7454,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9324,0.8387,0.0004</t>
-  </si>
-  <si>
-    <t>0.0125,0.8186,0.7380,0.0024</t>
-  </si>
-  <si>
-    <t>0.5105,0.4292,0.1249,0.0693</t>
-  </si>
-  <si>
-    <t>0.3394,0.5646,0.2093,0.0269</t>
-  </si>
-  <si>
-    <t>0.3403,0.0242,0.7125,0.0201</t>
-  </si>
-  <si>
-    <t>0.3828,0.4432,0.2284,0.0177</t>
-  </si>
-  <si>
-    <t>0.1991,0.0536,0.0716,0.7969</t>
-  </si>
-  <si>
-    <t>0.0125,0.0107,0.0217,0.9791</t>
-  </si>
-  <si>
-    <t>0.0218,0.0366,0.0183,0.9707</t>
-  </si>
-  <si>
-    <t>0.0491,0.0298,0.0242,0.9472</t>
-  </si>
-  <si>
-    <t>0.0003,0.9715,0.8097,0.0001</t>
-  </si>
-  <si>
-    <t>0.9750,0.0145,0.0016,0.0071</t>
-  </si>
-  <si>
-    <t>0.6606,0.3801,0.0442,0.0065</t>
-  </si>
-  <si>
-    <t>0.9479,0.0428,0.0032,0.0096</t>
-  </si>
-  <si>
-    <t>0.9390,0.0862,0.0041,0.0035</t>
-  </si>
-  <si>
-    <t>0.9348,0.0528,0.0030,0.0130</t>
-  </si>
-  <si>
-    <t>0.6944,0.0539,0.1333,0.1088</t>
-  </si>
-  <si>
-    <t>0.9538,0.0184,0.0027,0.0198</t>
-  </si>
-  <si>
-    <t>0.1339,0.5214,0.5165,0.0587</t>
-  </si>
-  <si>
-    <t>0.6299,0.0254,0.0461,0.2785</t>
-  </si>
-  <si>
-    <t>0.8932,0.0476,0.0386,0.0137</t>
-  </si>
-  <si>
-    <t>0.0950,0.9008,0.0494,0.0040</t>
-  </si>
-  <si>
-    <t>0.6631,0.4028,0.0338,0.0102</t>
-  </si>
-  <si>
-    <t>0.6693,0.3631,0.0649,0.0132</t>
-  </si>
-  <si>
-    <t>0.2606,0.7309,0.0626,0.0094</t>
-  </si>
-  <si>
-    <t>0.2645,0.7763,0.0471,0.0147</t>
-  </si>
-  <si>
-    <t>0.5303,0.4213,0.1222,0.0141</t>
-  </si>
-  <si>
-    <t>0.9826,0.0110,0.0020,0.0030</t>
-  </si>
-  <si>
-    <t>0.9857,0.0076,0.0010,0.0031</t>
-  </si>
-  <si>
-    <t>0.9862,0.0094,0.0015,0.0022</t>
-  </si>
-  <si>
-    <t>0.9875,0.0070,0.0013,0.0030</t>
-  </si>
-  <si>
-    <t>0.9870,0.0108,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9600,0.0445,0.0037,0.0028</t>
-  </si>
-  <si>
-    <t>0.9851,0.0060,0.0009,0.0043</t>
-  </si>
-  <si>
-    <t>0.9591,0.0342,0.0038,0.0063</t>
-  </si>
-  <si>
-    <t>0.1596,0.8664,0.0323,0.0025</t>
-  </si>
-  <si>
-    <t>0.7868,0.2787,0.0185,0.0021</t>
-  </si>
-  <si>
-    <t>0.5468,0.5410,0.0263,0.0025</t>
-  </si>
-  <si>
-    <t>0.7915,0.1767,0.0800,0.0087</t>
-  </si>
-  <si>
-    <t>0.5275,0.5864,0.0264,0.0044</t>
-  </si>
-  <si>
-    <t>0.9564,0.0360,0.0093,0.0041</t>
-  </si>
-  <si>
-    <t>0.9719,0.0279,0.0026,0.0024</t>
-  </si>
-  <si>
-    <t>0.9449,0.0693,0.0059,0.0029</t>
-  </si>
-  <si>
-    <t>0.1422,0.4150,0.4501,0.0026</t>
-  </si>
-  <si>
-    <t>0.8585,0.1657,0.0258,0.0055</t>
-  </si>
-  <si>
-    <t>0.0147,0.1893,0.9512,0.0019</t>
-  </si>
-  <si>
-    <t>0.0235,0.4807,0.8820,0.0057</t>
-  </si>
-  <si>
-    <t>0.0264,0.0817,0.9580,0.0016</t>
-  </si>
-  <si>
-    <t>0.0099,0.7992,0.7468,0.0043</t>
-  </si>
-  <si>
-    <t>0.0641,0.0555,0.9267,0.0022</t>
-  </si>
-  <si>
-    <t>0.0222,0.0384,0.9714,0.0017</t>
-  </si>
-  <si>
-    <t>0.0156,0.2208,0.9548,0.0008</t>
-  </si>
-  <si>
-    <t>0.1827,0.4569,0.4567,0.0114</t>
-  </si>
-  <si>
-    <t>0.0655,0.4334,0.7262,0.0045</t>
-  </si>
-  <si>
-    <t>0.3568,0.2661,0.3947,0.0173</t>
-  </si>
-  <si>
-    <t>0.2419,0.4543,0.3366,0.0085</t>
-  </si>
-  <si>
-    <t>0.1146,0.7200,0.2654,0.0092</t>
-  </si>
-  <si>
-    <t>0.3722,0.2498,0.4306,0.0290</t>
-  </si>
-  <si>
-    <t>0.2267,0.5337,0.3278,0.0206</t>
-  </si>
-  <si>
-    <t>0.3339,0.6266,0.1350,0.0225</t>
-  </si>
-  <si>
-    <t>0.5646,0.6051,0.0105,0.0014</t>
-  </si>
-  <si>
-    <t>0.5809,0.5887,0.0094,0.0013</t>
-  </si>
-  <si>
-    <t>0.8485,0.2508,0.0081,0.0028</t>
-  </si>
-  <si>
-    <t>0.9483,0.0496,0.0049,0.0046</t>
-  </si>
-  <si>
-    <t>0.9578,0.0509,0.0058,0.0035</t>
-  </si>
-  <si>
-    <t>0.4667,0.1572,0.4560,0.0351</t>
-  </si>
-  <si>
-    <t>0.5273,0.1313,0.3970,0.0409</t>
-  </si>
-  <si>
-    <t>0.4947,0.2590,0.3183,0.0572</t>
-  </si>
-  <si>
-    <t>0.5233,0.0963,0.4379,0.0368</t>
-  </si>
-  <si>
-    <t>0.3186,0.1021,0.6327,0.0226</t>
-  </si>
-  <si>
-    <t>0.0381,0.6359,0.6455,0.0076</t>
-  </si>
-  <si>
-    <t>0.0132,0.8096,0.7088,0.0040</t>
-  </si>
-  <si>
-    <t>0.0033,0.7240,0.9352,0.0006</t>
-  </si>
-  <si>
-    <t>0.0237,0.3563,0.9153,0.0020</t>
-  </si>
-  <si>
-    <t>0.0178,0.6393,0.8371,0.0037</t>
-  </si>
-  <si>
-    <t>0.9727,0.0336,0.0014,0.0020</t>
-  </si>
-  <si>
-    <t>0.9831,0.0145,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.9915,0.0073,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9851,0.0152,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.9919,0.0061,0.0006,0.0014</t>
-  </si>
-  <si>
-    <t>0.9935,0.0046,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9784,0.0124,0.0019,0.0060</t>
-  </si>
-  <si>
-    <t>0.9423,0.0604,0.0073,0.0049</t>
-  </si>
-  <si>
-    <t>0.1992,0.0289,0.8522,0.0072</t>
-  </si>
-  <si>
-    <t>0.5385,0.3610,0.1546,0.0114</t>
-  </si>
-  <si>
-    <t>0.8365,0.1156,0.0413,0.0267</t>
-  </si>
-  <si>
-    <t>0.0015,0.4121,0.9836,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.6586,0.9827,0.0001</t>
-  </si>
-  <si>
-    <t>0.0277,0.3349,0.8899,0.0049</t>
-  </si>
-  <si>
-    <t>0.0023,0.1927,0.9882,0.0003</t>
-  </si>
-  <si>
-    <t>0.1077,0.1436,0.8329,0.0128</t>
-  </si>
-  <si>
-    <t>0.0018,0.7252,0.9588,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.2666,0.9699,0.0006</t>
-  </si>
-  <si>
-    <t>0.2327,0.3381,0.5093,0.0099</t>
-  </si>
-  <si>
-    <t>0.3152,0.0826,0.6742,0.0159</t>
-  </si>
-  <si>
-    <t>0.5225,0.0845,0.4343,0.0921</t>
-  </si>
-  <si>
-    <t>0.6618,0.1174,0.2049,0.1225</t>
-  </si>
-  <si>
-    <t>0.9698,0.0392,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.9893,0.0096,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9841,0.0156,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.9819,0.0179,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.9845,0.0171,0.0013,0.0013</t>
-  </si>
-  <si>
-    <t>0.9846,0.0194,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9867,0.0125,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.0515,0.6353,0.6388,0.0094</t>
-  </si>
-  <si>
-    <t>0.0088,0.0999,0.9804,0.0007</t>
-  </si>
-  <si>
-    <t>0.0045,0.7720,0.8976,0.0007</t>
-  </si>
-  <si>
-    <t>0.1460,0.3048,0.6703,0.0219</t>
-  </si>
-  <si>
-    <t>0.0159,0.1363,0.9608,0.0021</t>
-  </si>
-  <si>
-    <t>0.3056,0.1645,0.6097,0.0729</t>
-  </si>
-  <si>
-    <t>0.2602,0.1886,0.5932,0.0237</t>
-  </si>
-  <si>
-    <t>0.0145,0.6022,0.8609,0.0035</t>
-  </si>
-  <si>
-    <t>0.4678,0.0232,0.0053,0.6098</t>
-  </si>
-  <si>
-    <t>0.0796,0.2196,0.0201,0.8897</t>
-  </si>
-  <si>
-    <t>0.0619,0.0704,0.0231,0.9320</t>
-  </si>
-  <si>
-    <t>0.0494,0.0172,0.0379,0.9394</t>
-  </si>
-  <si>
-    <t>0.0035,0.0049,0.0054,0.9946</t>
-  </si>
-  <si>
-    <t>0.4922,0.4198,0.0335,0.1188</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6465,0.2268,0.0817,0.1014</t>
+  </si>
+  <si>
+    <t>0.0534,0.0280,0.0167,0.9543</t>
+  </si>
+  <si>
+    <t>0.3343,0.3063,0.0116,0.3574</t>
+  </si>
+  <si>
+    <t>0.1387,0.1010,0.0300,0.8699</t>
+  </si>
+  <si>
+    <t>0.9816,0.0133,0.0015,0.0027</t>
+  </si>
+  <si>
+    <t>0.9882,0.0121,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9657,0.0430,0.0041,0.0017</t>
+  </si>
+  <si>
+    <t>0.9917,0.0066,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9872,0.0091,0.0008,0.0023</t>
+  </si>
+  <si>
+    <t>0.9888,0.0104,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9912,0.0102,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9848,0.0114,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.3019,0.4129,0.3092,0.0139</t>
+  </si>
+  <si>
+    <t>0.1655,0.4947,0.4639,0.0168</t>
+  </si>
+  <si>
+    <t>0.0385,0.2101,0.8926,0.0022</t>
+  </si>
+  <si>
+    <t>0.0443,0.1498,0.9159,0.0013</t>
+  </si>
+  <si>
+    <t>0.6259,0.1424,0.2521,0.0203</t>
+  </si>
+  <si>
+    <t>0.0349,0.9684,0.0148,0.0010</t>
+  </si>
+  <si>
+    <t>0.0952,0.8859,0.0786,0.0021</t>
+  </si>
+  <si>
+    <t>0.3650,0.6768,0.0500,0.0032</t>
+  </si>
+  <si>
+    <t>0.0363,0.9703,0.0093,0.0012</t>
+  </si>
+  <si>
+    <t>0.0214,0.9771,0.0238,0.0005</t>
+  </si>
+  <si>
+    <t>0.3811,0.0688,0.6187,0.0239</t>
+  </si>
+  <si>
+    <t>0.1235,0.5148,0.5344,0.0120</t>
+  </si>
+  <si>
+    <t>0.0117,0.0410,0.9798,0.0018</t>
+  </si>
+  <si>
+    <t>0.3158,0.1132,0.6353,0.0147</t>
+  </si>
+  <si>
+    <t>0.1199,0.1335,0.8240,0.0059</t>
+  </si>
+  <si>
+    <t>0.1634,0.1959,0.7436,0.0204</t>
+  </si>
+  <si>
+    <t>0.0118,0.0353,0.9815,0.0007</t>
+  </si>
+  <si>
+    <t>0.2038,0.8443,0.0175,0.0065</t>
+  </si>
+  <si>
+    <t>0.4283,0.3259,0.3438,0.0239</t>
+  </si>
+  <si>
+    <t>0.0147,0.0602,0.9708,0.0017</t>
+  </si>
+  <si>
+    <t>0.0428,0.8877,0.1919,0.0036</t>
+  </si>
+  <si>
+    <t>0.4789,0.5608,0.0863,0.0208</t>
+  </si>
+  <si>
+    <t>0.3104,0.2776,0.4428,0.0187</t>
+  </si>
+  <si>
+    <t>0.2915,0.7873,0.0224,0.0028</t>
+  </si>
+  <si>
+    <t>0.1935,0.8126,0.0750,0.0217</t>
+  </si>
+  <si>
+    <t>0.0018,0.9637,0.4471,0.0020</t>
+  </si>
+  <si>
+    <t>0.0052,0.7312,0.9183,0.0008</t>
+  </si>
+  <si>
+    <t>0.0135,0.6927,0.8682,0.0016</t>
+  </si>
+  <si>
+    <t>0.0350,0.4370,0.8618,0.0037</t>
+  </si>
+  <si>
+    <t>0.0060,0.7807,0.8763,0.0010</t>
+  </si>
+  <si>
+    <t>0.0062,0.9803,0.0481,0.0005</t>
+  </si>
+  <si>
+    <t>0.0262,0.6942,0.7618,0.0038</t>
+  </si>
+  <si>
+    <t>0.4003,0.5064,0.0932,0.1846</t>
+  </si>
+  <si>
+    <t>0.0030,0.9873,0.0083,0.0086</t>
+  </si>
+  <si>
+    <t>0.0064,0.9858,0.0354,0.0007</t>
+  </si>
+  <si>
+    <t>0.0059,0.9874,0.0295,0.0006</t>
+  </si>
+  <si>
+    <t>0.0140,0.6707,0.8419,0.0052</t>
+  </si>
+  <si>
+    <t>0.0043,0.7803,0.9154,0.0007</t>
+  </si>
+  <si>
+    <t>0.2059,0.0640,0.7842,0.0161</t>
+  </si>
+  <si>
+    <t>0.1029,0.1699,0.8222,0.0088</t>
+  </si>
+  <si>
+    <t>0.0158,0.3997,0.9205,0.0053</t>
+  </si>
+  <si>
+    <t>0.0064,0.2093,0.9733,0.0005</t>
+  </si>
+  <si>
+    <t>0.9826,0.0192,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.6050,0.4264,0.0533,0.0051</t>
+  </si>
+  <si>
+    <t>0.9866,0.0091,0.0007,0.0024</t>
+  </si>
+  <si>
+    <t>0.0728,0.1334,0.8736,0.0061</t>
+  </si>
+  <si>
+    <t>0.9085,0.1176,0.0073,0.0061</t>
+  </si>
+  <si>
+    <t>0.9857,0.0180,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9883,0.0098,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0014,0.9546,0.7687,0.0005</t>
+  </si>
+  <si>
+    <t>0.0142,0.7099,0.8301,0.0048</t>
+  </si>
+  <si>
+    <t>0.0035,0.7717,0.9097,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.9828,0.4034,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.2854,0.9870,0.0002</t>
+  </si>
+  <si>
+    <t>0.0219,0.9379,0.1732,0.0021</t>
+  </si>
+  <si>
+    <t>0.0018,0.9965,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.4691,0.0824,0.5099,0.0282</t>
+  </si>
+  <si>
+    <t>0.2689,0.7082,0.1150,0.0093</t>
+  </si>
+  <si>
+    <t>0.0995,0.6160,0.3828,0.0157</t>
+  </si>
+  <si>
+    <t>0.0019,0.9418,0.7882,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.8554,0.8995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0026,0.9487,0.7034,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9757,0.6800,0.0003</t>
+  </si>
+  <si>
+    <t>0.3085,0.3059,0.0647,0.5192</t>
+  </si>
+  <si>
+    <t>0.0223,0.0474,0.0061,0.9760</t>
+  </si>
+  <si>
+    <t>0.0073,0.0192,0.0050,0.9904</t>
+  </si>
+  <si>
+    <t>0.0511,0.0636,0.0161,0.9497</t>
+  </si>
+  <si>
+    <t>0.0820,0.1222,0.0491,0.8870</t>
+  </si>
+  <si>
+    <t>0.0174,0.0419,0.0102,0.9772</t>
+  </si>
+  <si>
+    <t>0.0017,0.9578,0.7244,0.0006</t>
+  </si>
+  <si>
+    <t>0.0016,0.9216,0.8878,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.9213,0.8190,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.9042,0.9017,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.9548,0.8586,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.9119,0.7121,0.0016</t>
+  </si>
+  <si>
+    <t>0.9904,0.0082,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9797,0.0209,0.0023,0.0023</t>
+  </si>
+  <si>
+    <t>0.9802,0.0208,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.9909,0.0104,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9858,0.0133,0.0012,0.0018</t>
+  </si>
+  <si>
+    <t>0.9955,0.0039,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9787,0.0271,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.9858,0.0115,0.0013,0.0020</t>
+  </si>
+  <si>
+    <t>0.9936,0.0040,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9890,0.0084,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9927,0.0056,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9918,0.0091,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9858,0.0129,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.9937,0.0045,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9897,0.0105,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9942,0.0033,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.0494,0.0475,0.9370,0.0069</t>
+  </si>
+  <si>
+    <t>0.0207,0.1935,0.9445,0.0012</t>
+  </si>
+  <si>
+    <t>0.4057,0.2552,0.4478,0.0689</t>
+  </si>
+  <si>
+    <t>0.2022,0.3034,0.6132,0.0235</t>
+  </si>
+  <si>
+    <t>0.0500,0.9556,0.0172,0.0008</t>
+  </si>
+  <si>
+    <t>0.0259,0.9712,0.0289,0.0008</t>
+  </si>
+  <si>
+    <t>0.4641,0.6786,0.0163,0.0021</t>
+  </si>
+  <si>
+    <t>0.6161,0.5244,0.0148,0.0018</t>
+  </si>
+  <si>
+    <t>0.1239,0.8952,0.0244,0.0014</t>
+  </si>
+  <si>
+    <t>0.0169,0.9829,0.0112,0.0003</t>
+  </si>
+  <si>
+    <t>0.5310,0.6063,0.0160,0.0021</t>
+  </si>
+  <si>
+    <t>0.1595,0.8162,0.0894,0.0184</t>
+  </si>
+  <si>
+    <t>0.2453,0.1938,0.6426,0.0101</t>
+  </si>
+  <si>
+    <t>0.5045,0.2904,0.2687,0.0755</t>
+  </si>
+  <si>
+    <t>0.4852,0.1398,0.3969,0.0137</t>
+  </si>
+  <si>
+    <t>0.6011,0.2660,0.1385,0.0798</t>
+  </si>
+  <si>
+    <t>0.0158,0.9776,0.0275,0.0016</t>
+  </si>
+  <si>
+    <t>0.0120,0.9732,0.0472,0.0025</t>
+  </si>
+  <si>
+    <t>0.1904,0.7460,0.1339,0.0138</t>
+  </si>
+  <si>
+    <t>0.0009,0.9959,0.0276,0.0002</t>
+  </si>
+  <si>
+    <t>0.0267,0.9629,0.0485,0.0006</t>
+  </si>
+  <si>
+    <t>0.5576,0.5478,0.0269,0.0047</t>
+  </si>
+  <si>
+    <t>0.7074,0.4114,0.0152,0.0029</t>
+  </si>
+  <si>
+    <t>0.9719,0.0276,0.0034,0.0027</t>
+  </si>
+  <si>
+    <t>0.9708,0.0373,0.0028,0.0022</t>
+  </si>
+  <si>
+    <t>0.9808,0.0098,0.0014,0.0060</t>
+  </si>
+  <si>
+    <t>0.9679,0.0294,0.0046,0.0038</t>
+  </si>
+  <si>
+    <t>0.9887,0.0100,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9665,0.0378,0.0046,0.0019</t>
+  </si>
+  <si>
+    <t>0.9846,0.0125,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.9553,0.0419,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.0011,0.9510,0.8366,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9682,0.6411,0.0005</t>
+  </si>
+  <si>
+    <t>0.0037,0.8212,0.8875,0.0007</t>
+  </si>
+  <si>
+    <t>0.0061,0.7891,0.8578,0.0014</t>
+  </si>
+  <si>
+    <t>0.2992,0.5921,0.1905,0.0202</t>
+  </si>
+  <si>
+    <t>0.3603,0.2193,0.4637,0.0223</t>
+  </si>
+  <si>
+    <t>0.3322,0.0618,0.6711,0.0098</t>
+  </si>
+  <si>
+    <t>0.4813,0.3649,0.2185,0.0327</t>
+  </si>
+  <si>
+    <t>0.2711,0.0648,0.0606,0.7479</t>
+  </si>
+  <si>
+    <t>0.0042,0.0081,0.0066,0.9932</t>
+  </si>
+  <si>
+    <t>0.0299,0.0129,0.0454,0.9520</t>
+  </si>
+  <si>
+    <t>0.0288,0.0395,0.0080,0.9697</t>
+  </si>
+  <si>
+    <t>0.0005,0.9717,0.7486,0.0003</t>
+  </si>
+  <si>
+    <t>0.9543,0.0360,0.0016,0.0115</t>
+  </si>
+  <si>
+    <t>0.5875,0.4847,0.0352,0.0047</t>
+  </si>
+  <si>
+    <t>0.9481,0.0810,0.0017,0.0035</t>
+  </si>
+  <si>
+    <t>0.7106,0.3706,0.0216,0.0058</t>
+  </si>
+  <si>
+    <t>0.9366,0.0594,0.0131,0.0061</t>
+  </si>
+  <si>
+    <t>0.6277,0.3390,0.0598,0.0765</t>
+  </si>
+  <si>
+    <t>0.9612,0.0141,0.0013,0.0161</t>
+  </si>
+  <si>
+    <t>0.2054,0.2781,0.6408,0.0460</t>
+  </si>
+  <si>
+    <t>0.7650,0.0176,0.0400,0.1732</t>
+  </si>
+  <si>
+    <t>0.9444,0.0280,0.0062,0.0155</t>
+  </si>
+  <si>
+    <t>0.0907,0.9179,0.0261,0.0062</t>
+  </si>
+  <si>
+    <t>0.7294,0.2642,0.0397,0.0339</t>
+  </si>
+  <si>
+    <t>0.6815,0.3582,0.0510,0.0173</t>
+  </si>
+  <si>
+    <t>0.2240,0.8041,0.0561,0.0109</t>
+  </si>
+  <si>
+    <t>0.6769,0.2704,0.1044,0.0125</t>
+  </si>
+  <si>
+    <t>0.5861,0.4686,0.0464,0.0105</t>
+  </si>
+  <si>
+    <t>0.9817,0.0150,0.0017,0.0026</t>
+  </si>
+  <si>
+    <t>0.9853,0.0135,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.9660,0.0383,0.0026,0.0034</t>
+  </si>
+  <si>
+    <t>0.9387,0.0494,0.0117,0.0080</t>
+  </si>
+  <si>
+    <t>0.9519,0.0509,0.0039,0.0068</t>
+  </si>
+  <si>
+    <t>0.9876,0.0046,0.0005,0.0046</t>
+  </si>
+  <si>
+    <t>0.9876,0.0070,0.0009,0.0033</t>
+  </si>
+  <si>
+    <t>0.9830,0.0106,0.0008,0.0041</t>
+  </si>
+  <si>
+    <t>0.1931,0.8532,0.0325,0.0026</t>
+  </si>
+  <si>
+    <t>0.8328,0.2632,0.0082,0.0020</t>
+  </si>
+  <si>
+    <t>0.5082,0.6309,0.0128,0.0044</t>
+  </si>
+  <si>
+    <t>0.4889,0.4067,0.1650,0.0070</t>
+  </si>
+  <si>
+    <t>0.9428,0.0798,0.0073,0.0020</t>
+  </si>
+  <si>
+    <t>0.9561,0.0379,0.0057,0.0054</t>
+  </si>
+  <si>
+    <t>0.9800,0.0153,0.0018,0.0031</t>
+  </si>
+  <si>
+    <t>0.6876,0.2802,0.0656,0.0044</t>
+  </si>
+  <si>
+    <t>0.0330,0.2243,0.9039,0.0019</t>
+  </si>
+  <si>
+    <t>0.7068,0.3299,0.0398,0.0038</t>
+  </si>
+  <si>
+    <t>0.0046,0.1286,0.9849,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.6179,0.9309,0.0006</t>
+  </si>
+  <si>
+    <t>0.3680,0.1218,0.5512,0.0158</t>
+  </si>
+  <si>
+    <t>0.0156,0.7769,0.6920,0.0073</t>
+  </si>
+  <si>
+    <t>0.0217,0.2323,0.9320,0.0014</t>
+  </si>
+  <si>
+    <t>0.0343,0.0463,0.9557,0.0012</t>
+  </si>
+  <si>
+    <t>0.0257,0.1223,0.9451,0.0016</t>
+  </si>
+  <si>
+    <t>0.2461,0.4592,0.3729,0.0131</t>
+  </si>
+  <si>
+    <t>0.1343,0.0709,0.8649,0.0031</t>
+  </si>
+  <si>
+    <t>0.2747,0.7392,0.0876,0.0127</t>
+  </si>
+  <si>
+    <t>0.1865,0.5923,0.3173,0.0115</t>
+  </si>
+  <si>
+    <t>0.1501,0.4704,0.5068,0.0078</t>
+  </si>
+  <si>
+    <t>0.1333,0.7004,0.2661,0.0165</t>
+  </si>
+  <si>
+    <t>0.4914,0.2596,0.3219,0.0345</t>
+  </si>
+  <si>
+    <t>0.3203,0.6117,0.1296,0.0312</t>
+  </si>
+  <si>
+    <t>0.8862,0.1848,0.0066,0.0016</t>
+  </si>
+  <si>
+    <t>0.8684,0.2207,0.0077,0.0015</t>
+  </si>
+  <si>
+    <t>0.9256,0.1319,0.0030,0.0031</t>
+  </si>
+  <si>
+    <t>0.9817,0.0163,0.0021,0.0022</t>
+  </si>
+  <si>
+    <t>0.9195,0.1265,0.0071,0.0021</t>
+  </si>
+  <si>
+    <t>0.2225,0.7179,0.1540,0.0224</t>
+  </si>
+  <si>
+    <t>0.4079,0.4369,0.2288,0.0282</t>
+  </si>
+  <si>
+    <t>0.4888,0.3805,0.2097,0.0994</t>
+  </si>
+  <si>
+    <t>0.5230,0.0882,0.4233,0.0367</t>
+  </si>
+  <si>
+    <t>0.5172,0.1036,0.4136,0.0513</t>
+  </si>
+  <si>
+    <t>0.0105,0.3973,0.9080,0.0020</t>
+  </si>
+  <si>
+    <t>0.0108,0.7948,0.7885,0.0028</t>
+  </si>
+  <si>
+    <t>0.0066,0.7407,0.8940,0.0015</t>
+  </si>
+  <si>
+    <t>0.0099,0.5102,0.9353,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.8878,0.8738,0.0005</t>
+  </si>
+  <si>
+    <t>0.9797,0.0203,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.9842,0.0171,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9830,0.0147,0.0022,0.0020</t>
+  </si>
+  <si>
+    <t>0.9844,0.0141,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.9849,0.0154,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9893,0.0095,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9886,0.0071,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9781,0.0211,0.0029,0.0022</t>
+  </si>
+  <si>
+    <t>0.2048,0.0373,0.8211,0.0062</t>
+  </si>
+  <si>
+    <t>0.4510,0.1472,0.4511,0.0122</t>
+  </si>
+  <si>
+    <t>0.8940,0.0871,0.0277,0.0072</t>
+  </si>
+  <si>
+    <t>0.0045,0.1827,0.9827,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.8355,0.8407,0.0013</t>
+  </si>
+  <si>
+    <t>0.0642,0.3451,0.7850,0.0054</t>
+  </si>
+  <si>
+    <t>0.0111,0.1551,0.9694,0.0011</t>
+  </si>
+  <si>
+    <t>0.0242,0.2839,0.9088,0.0019</t>
+  </si>
+  <si>
+    <t>0.0030,0.7021,0.9460,0.0004</t>
+  </si>
+  <si>
+    <t>0.0190,0.3505,0.9224,0.0019</t>
+  </si>
+  <si>
+    <t>0.1097,0.6534,0.3698,0.0108</t>
+  </si>
+  <si>
+    <t>0.3832,0.0432,0.6356,0.0163</t>
+  </si>
+  <si>
+    <t>0.4219,0.0451,0.6046,0.0145</t>
+  </si>
+  <si>
+    <t>0.4442,0.3190,0.2948,0.0363</t>
+  </si>
+  <si>
+    <t>0.9659,0.0452,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9877,0.0096,0.0013,0.0018</t>
+  </si>
+  <si>
+    <t>0.9896,0.0092,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.9709,0.0358,0.0028,0.0022</t>
+  </si>
+  <si>
+    <t>0.9862,0.0115,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9867,0.0126,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9907,0.0080,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9893,0.0116,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0346,0.2570,0.8978,0.0029</t>
+  </si>
+  <si>
+    <t>0.0045,0.5030,0.9554,0.0006</t>
+  </si>
+  <si>
+    <t>0.0049,0.7596,0.8896,0.0013</t>
+  </si>
+  <si>
+    <t>0.1822,0.1861,0.7069,0.0097</t>
+  </si>
+  <si>
+    <t>0.0349,0.1975,0.9143,0.0038</t>
+  </si>
+  <si>
+    <t>0.4558,0.1064,0.4817,0.0426</t>
+  </si>
+  <si>
+    <t>0.0849,0.5229,0.6183,0.0102</t>
+  </si>
+  <si>
+    <t>0.0274,0.3693,0.9029,0.0044</t>
+  </si>
+  <si>
+    <t>0.8235,0.0265,0.0161,0.1252</t>
+  </si>
+  <si>
+    <t>0.0756,0.1323,0.0379,0.9017</t>
+  </si>
+  <si>
+    <t>0.2125,0.0423,0.0552,0.7970</t>
+  </si>
+  <si>
+    <t>0.0858,0.0929,0.0179,0.9115</t>
+  </si>
+  <si>
+    <t>0.0276,0.0113,0.0114,0.9747</t>
+  </si>
+  <si>
+    <t>0.6220,0.2583,0.0657,0.1287</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +2001,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2141,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2169,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2421,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>263</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>263</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>263</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>263</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>263</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2855,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2939,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3499,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3541,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>263</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4115,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4213,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4409,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4465,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4507,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4717,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4843,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4885,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>263</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>263</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5193,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5207,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5333,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5347,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5417,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5431,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5445,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
